--- a/src/node/uploads/red.xlsx
+++ b/src/node/uploads/red.xlsx
@@ -44,7 +44,7 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss\ \U\T\C"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -1010,7 +1010,7 @@
   <dimension ref="A1:B1369"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="24.125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="39.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
